--- a/amostras/principal/P30/matriz_rastreabilidade_P30.xlsx
+++ b/amostras/principal/P30/matriz_rastreabilidade_P30.xlsx
@@ -1439,28 +1439,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
@@ -1497,28 +1497,28 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
